--- a/jira_export_2026-07-17.xlsx
+++ b/jira_export_2026-07-17.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>364 h</t>
+          <t>375 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>100</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>133.33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>1944</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>228.71</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17">
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>90</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25">
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>1505</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>463.08</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31">
@@ -3022,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>219.1</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>109.55</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="33">
@@ -3886,7 +3886,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>1028.4</v>
       </c>
       <c r="P51" s="13" t="n">
-        <v>373.96</v>
+        <v>342.8</v>
       </c>
     </row>
     <row r="52">
@@ -4886,7 +4886,7 @@
         <v>3</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>4224.5</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>1207</v>
+        <v>649.92</v>
       </c>
     </row>
     <row r="59">
@@ -4958,7 +4958,7 @@
         <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>1942.2</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>517.92</v>
+        <v>485.55</v>
       </c>
     </row>
     <row r="60">
@@ -6398,7 +6398,7 @@
         <v>4</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>200</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80">
@@ -11662,7 +11662,7 @@
         <v>19</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>19</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>27</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>34</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>30037.3</v>
       </c>
       <c r="P176" s="19" t="n">
-        <v>132.91</v>
+        <v>127.69</v>
       </c>
     </row>
   </sheetData>
@@ -13927,7 +13927,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>119.25</v>
+        <v>122.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>31.75</v>
@@ -13936,7 +13936,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>154</v>
+        <v>157.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>41</v>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>63.5</v>
+        <v>69.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -13966,7 +13966,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>70.25</v>
+        <v>76.25</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15</v>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>78.58</v>
+        <v>80.83</v>
       </c>
     </row>
   </sheetData>
@@ -14076,13 +14076,13 @@
         <v>393796</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>208741</v>
+        <v>207864</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>185055</v>
+        <v>185931</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>147749</v>
+        <v>148625</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
@@ -14101,13 +14101,13 @@
         <v>183955</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>79398</v>
+        <v>78522</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>104557</v>
+        <v>105433</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>90259</v>
+        <v>91135</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>10060</v>

--- a/jira_export_2026-07-17.xlsx
+++ b/jira_export_2026-07-17.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>30,037 €</t>
+          <t>34,056 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,14 +769,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>8,455 €</t>
+          <t>8,527 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>21,582 €</t>
+          <t>25,529 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>375 h</t>
+          <t>381 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>80</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6">
@@ -1902,10 +1902,10 @@
         <v>1296</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>1944</v>
+        <v>2016</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17">
@@ -2182,10 +2182,10 @@
         <v>3207.7</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>4170.01</v>
+        <v>5453.09</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>926.67</v>
+        <v>1211.8</v>
       </c>
     </row>
     <row r="21">
@@ -2254,10 +2254,10 @@
         <v>848.7</v>
       </c>
       <c r="O21" s="17" t="n">
-        <v>141.45</v>
+        <v>721.395</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>35.36</v>
+        <v>180.35</v>
       </c>
     </row>
     <row r="22">
@@ -2470,10 +2470,10 @@
         <v>280</v>
       </c>
       <c r="O24" s="17" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>180</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25">
@@ -3614,10 +3614,10 @@
         <v>4040</v>
       </c>
       <c r="O40" s="17" t="n">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0</v>
+        <v>1346.67</v>
       </c>
     </row>
     <row r="41">
@@ -4974,10 +4974,10 @@
         <v>1618.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>1942.2</v>
+        <v>1996.15</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>485.55</v>
+        <v>499.04</v>
       </c>
     </row>
     <row r="60">
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80">
@@ -9812,7 +9812,7 @@
         <v>10</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>10</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
@@ -12990,10 +12990,10 @@
         <v>69305.66</v>
       </c>
       <c r="O176" s="19" t="n">
-        <v>30037.3</v>
+        <v>34056.275</v>
       </c>
       <c r="P176" s="19" t="n">
-        <v>127.69</v>
+        <v>143.24</v>
       </c>
     </row>
   </sheetData>
@@ -13927,7 +13927,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>122.5</v>
+        <v>125</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>31.75</v>
@@ -13936,17 +13936,17 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>157.25</v>
+        <v>159.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>41</v>
+        <v>43.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>80.83</v>
+        <v>81.83</v>
       </c>
     </row>
   </sheetData>
@@ -14073,10 +14073,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>393796</v>
+        <v>389777</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>207864</v>
+        <v>203845</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>185931</v>
@@ -14098,10 +14098,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>183955</v>
+        <v>183883</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>78522</v>
+        <v>78450</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>105433</v>
@@ -14123,10 +14123,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>209840</v>
+        <v>205893</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>129342</v>
+        <v>125395</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>80498</v>
